--- a/Result/profitability/8077.xlsx
+++ b/Result/profitability/8077.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="N2" t="n">
-        <v>26.05625</v>
+        <v>26.8725</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-3.14</v>
       </c>
       <c r="M3" t="n">
-        <v>0.86375</v>
+        <v>0.7637499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>20.665</v>
+        <v>19.59125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-4.41</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04874999999999985</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="N4" t="n">
-        <v>8.286250000000001</v>
+        <v>7.829999999999998</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-3.45</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5650000000000002</v>
+        <v>-0.5337500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01750000000000096</v>
+        <v>-0.04000000000000092</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-3.44</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1275</v>
+        <v>-1.00625</v>
       </c>
       <c r="N6" t="n">
-        <v>-9.978750000000002</v>
+        <v>-9.07375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-5.21</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.82125</v>
+        <v>-2.05375</v>
       </c>
       <c r="N7" t="n">
-        <v>-24.65375</v>
+        <v>-25.81375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5125</v>
+        <v>-2.5925</v>
       </c>
       <c r="N8" t="n">
-        <v>-33.10625</v>
+        <v>-33.57875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8077</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>267</v>
+      </c>
+      <c r="D75" t="n">
+        <v>195</v>
+      </c>
+      <c r="E75" t="n">
+        <v>72</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="G75" t="n">
+        <v>41</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.22%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>32</v>
+      </c>
+      <c r="K75" t="n">
+        <v>29</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.44875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.38375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.6399999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3282051282051281</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.779999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1231270358306188</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2358490566037736</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.1799999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.006642066420664228</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
